--- a/tame_output/ON/bt/strategyON_20240217.xlsx
+++ b/tame_output/ON/bt/strategyON_20240217.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.0%</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1875"/>
+  <dimension ref="A1:G1876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.505294946706487</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44686,6 +44686,29 @@
       </c>
       <c r="G1875" t="n">
         <v>4.475644586352897</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="2" t="n">
+        <v>45338</v>
+      </c>
+      <c r="B1876" t="n">
+        <v>3.50044609677668</v>
+      </c>
+      <c r="C1876" t="n">
+        <v>3.131913338815032</v>
+      </c>
+      <c r="D1876" t="n">
+        <v>1.593763110705267</v>
+      </c>
+      <c r="E1876" t="n">
+        <v>3.769062158783392</v>
+      </c>
+      <c r="F1876" t="n">
+        <v>2.251097810392948</v>
+      </c>
+      <c r="G1876" t="n">
+        <v>4.482572025050802</v>
       </c>
     </row>
   </sheetData>
